--- a/artfynd/A 53296-2024 artfynd.xlsx
+++ b/artfynd/A 53296-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113178707</v>
+        <v>113178705</v>
       </c>
       <c r="B2" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>605329</v>
+        <v>605321</v>
       </c>
       <c r="R2" t="n">
-        <v>6955247</v>
+        <v>6955160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,11 +763,11 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3 substratenheter # förrötade granlågor</t>
+          <t>2 substratenheter # förrötade granlågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113178712</v>
+        <v>113178707</v>
       </c>
       <c r="B3" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>605395</v>
+        <v>605329</v>
       </c>
       <c r="R3" t="n">
-        <v>6955250</v>
+        <v>6955247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,15 +873,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ca 90-årig barrblandskog med aspinslag</t>
+          <t>relativt gammal barrnaturskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad grövre granlåga</t>
+          <t>3 substratenheter # förrötade granlågor</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -916,12 +906,7 @@
         <v>113178710</v>
       </c>
       <c r="B4" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,12 +923,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1032,15 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113178708</v>
+        <v>113178713</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +1028,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>605373</v>
+        <v>605310</v>
       </c>
       <c r="R5" t="n">
-        <v>6955265</v>
+        <v>6955314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1101,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>ca 90-årig barrblandskog med aspinslag</t>
+          <t>Asprik äldre barrblandskog</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1151,15 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113178713</v>
+        <v>113178714</v>
       </c>
       <c r="B6" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,12 +1151,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>605310</v>
+        <v>605311</v>
       </c>
       <c r="R6" t="n">
-        <v>6955314</v>
+        <v>6955372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1215,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Asprik äldre barrblandskog</t>
+          <t>Asprik ca 130-årig barrblandskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1248,7 +1223,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+          <t>1 substratenheter # grov förrötad granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113178714</v>
+        <v>113178708</v>
       </c>
       <c r="B7" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>605311</v>
+        <v>605373</v>
       </c>
       <c r="R7" t="n">
-        <v>6955372</v>
+        <v>6955265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1329,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Asprik ca 130-årig barrblandskog</t>
+          <t>ca 90-årig barrblandskog med aspinslag</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1367,7 +1337,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov förrötad granlåga</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,12 +1362,7 @@
         <v>113178711</v>
       </c>
       <c r="B8" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,59 +1473,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113178703</v>
+        <v>113178704</v>
       </c>
       <c r="B9" t="n">
-        <v>89869</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5747</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Herrgårdsbergets nordsida, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>605334</v>
+        <v>605316</v>
       </c>
       <c r="R9" t="n">
-        <v>6955362</v>
+        <v>6955123</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1606,7 +1557,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>stigskärning i äldre barrblandskog</t>
+          <t>relativt gammal barrnaturskog med tallöverståndare</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Grov förrötad granlåg</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1628,19 +1587,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113178704</v>
+        <v>113178712</v>
       </c>
       <c r="B10" t="n">
-        <v>90774</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1653,12 +1607,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>605316</v>
+        <v>605395</v>
       </c>
       <c r="R10" t="n">
-        <v>6955123</v>
+        <v>6955250</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1671,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog med tallöverståndare</t>
+          <t>ca 90-årig barrblandskog med aspinslag</t>
         </is>
       </c>
       <c r="AN10" t="n">
@@ -1725,7 +1679,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # Grov förrötad granlåg</t>
+          <t>1 substratenheter # förrötad grövre granlåga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1747,50 +1701,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113178705</v>
+        <v>113178703</v>
       </c>
       <c r="B11" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>5747</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Herrgårdsbergets nordsida, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>605321</v>
+        <v>605334</v>
       </c>
       <c r="R11" t="n">
-        <v>6955160</v>
+        <v>6955362</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,15 +1794,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>relativt gammal barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>2 substratenheter # förrötade granlågor</t>
+          <t>stigskärning i äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 53296-2024 artfynd.xlsx
+++ b/artfynd/A 53296-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178705</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178710</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178713</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178708</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178704</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178712</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1813,8 +1863,25 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>